--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hulumulu\Desktop\Никита\Лаб.работа\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58948580-98B9-4CB8-A3B5-871BC79B21D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23258" windowHeight="12578"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -310,7 +309,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -731,6 +730,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -779,15 +790,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -795,9 +797,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -893,23 +892,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -945,23 +927,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1137,33 +1102,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:Y49"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="116.77734375" customWidth="1"/>
+    <col min="1" max="1" width="116.796875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="4" max="4" width="14.46484375" customWidth="1"/>
+    <col min="6" max="6" width="17.46484375" customWidth="1"/>
+    <col min="8" max="8" width="13.53125" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" customWidth="1"/>
+    <col min="12" max="12" width="14.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-    </row>
-    <row r="5" spans="1:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.5">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+    </row>
+    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1174,7 +1139,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="24.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="25.15" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
         <v>13</v>
@@ -1200,7 +1165,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
         <v>8</v>
       </c>
@@ -1233,34 +1198,34 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-    </row>
-    <row r="9" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
+    </row>
+    <row r="9" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="31">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="9">
-        <v>116</v>
+      <c r="D9" s="31">
+        <v>140</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9">
@@ -1275,37 +1240,37 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="31">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="9">
-        <v>96</v>
+      <c r="D11" s="31">
+        <v>120</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9">
@@ -1320,21 +1285,21 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
-    </row>
-    <row r="13" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
+    </row>
+    <row r="13" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
         <v>21</v>
       </c>
@@ -1366,21 +1331,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
-    </row>
-    <row r="15" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
+    </row>
+    <row r="15" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
         <v>20</v>
       </c>
@@ -1413,41 +1378,37 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
-    </row>
-    <row r="17" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
+    </row>
+    <row r="17" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="31">
-        <f>B11</f>
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9">
-        <f>D11</f>
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9">
-        <f>F11</f>
         <v>102</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9">
-        <f>H11</f>
         <v>80</v>
       </c>
       <c r="I17" s="9"/>
@@ -1462,21 +1423,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
-    </row>
-    <row r="19" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
+    </row>
+    <row r="19" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
         <v>26</v>
       </c>
@@ -1507,21 +1468,21 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
-    </row>
-    <row r="21" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
+    </row>
+    <row r="21" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
@@ -1552,21 +1513,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
-    </row>
-    <row r="23" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
+    </row>
+    <row r="23" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
@@ -1594,21 +1555,21 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
+    </row>
+    <row r="25" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
         <v>23</v>
       </c>
@@ -1640,21 +1601,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
-    </row>
-    <row r="27" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
+    </row>
+    <row r="27" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
         <v>27</v>
       </c>
@@ -1682,21 +1643,21 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
-    </row>
-    <row r="29" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
+    </row>
+    <row r="29" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A29" s="27" t="s">
         <v>7</v>
       </c>
@@ -1730,21 +1691,21 @@
         <v>990</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
-    </row>
-    <row r="31" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
+    </row>
+    <row r="31" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A31" s="27" t="s">
         <v>11</v>
       </c>
@@ -1778,32 +1739,32 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
-    </row>
-    <row r="33" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
+    </row>
+    <row r="33" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A33" s="27" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="11">
         <f>B17/(1-B21)</f>
-        <v>105.55555555555556</v>
+        <v>122.22222222222221</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11">
         <f>D17/(1-D21)</f>
-        <v>106.66666666666666</v>
+        <v>122.22222222222221</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11">
@@ -1826,32 +1787,32 @@
         <v>88.888888888888886</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
-    </row>
-    <row r="35" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
+    </row>
+    <row r="35" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A35" s="27" t="s">
         <v>0</v>
       </c>
       <c r="B35" s="10">
         <f>B33-B17</f>
-        <v>10.555555555555557</v>
+        <v>12.222222222222214</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10">
         <f t="shared" ref="D35:J35" si="0">D33-D17</f>
-        <v>10.666666666666657</v>
+        <v>12.222222222222214</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10">
@@ -1874,32 +1835,32 @@
         <v>8.8888888888888857</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-    </row>
-    <row r="37" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+    </row>
+    <row r="37" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A37" s="27" t="s">
         <v>9</v>
       </c>
       <c r="B37" s="10">
         <f>(B17+B33)/2</f>
-        <v>100.27777777777777</v>
+        <v>116.11111111111111</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11">
         <f>(D17+D33)/2</f>
-        <v>101.33333333333333</v>
+        <v>116.11111111111111</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="12">
@@ -1922,37 +1883,37 @@
         <v>84.444444444444443</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
-    </row>
-    <row r="39" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
+    </row>
+    <row r="39" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A39" s="27" t="s">
         <v>19</v>
       </c>
       <c r="B39" s="10">
         <f>B23*(B9*B9-B11*B11)</f>
-        <v>13188</v>
+        <v>16328</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11">
         <f>D23*(D9*D9-D11*D11)</f>
-        <v>13313.6</v>
+        <v>16328</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="12">
         <f>F23*(F9*F9-F11*F11)</f>
-        <v>29757.780000000002</v>
+        <v>30144</v>
       </c>
       <c r="G39" s="11"/>
       <c r="H39" s="12">
@@ -1970,37 +1931,37 @@
         <v>9340.7150000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
-    </row>
-    <row r="41" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
+    </row>
+    <row r="41" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
         <v>10</v>
       </c>
       <c r="B41" s="10">
         <f>B15*B39</f>
-        <v>19782</v>
+        <v>24492</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11">
         <f>D15*D39</f>
-        <v>19970.400000000001</v>
+        <v>24492</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="12">
         <f>F15*F39</f>
-        <v>44636.670000000006</v>
+        <v>45216</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="12">
@@ -2018,37 +1979,37 @@
         <v>14011.0725</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
-    </row>
-    <row r="43" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
+    </row>
+    <row r="43" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
         <v>5</v>
       </c>
       <c r="B43" s="10">
         <f>B41/1.2</f>
-        <v>16485</v>
+        <v>20410</v>
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11">
         <f t="shared" ref="D43:J43" si="1">D41/1.2</f>
-        <v>16642.000000000004</v>
+        <v>20410</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="12">
         <f t="shared" si="1"/>
-        <v>37197.225000000006</v>
+        <v>37680</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="12">
@@ -2066,37 +2027,37 @@
         <v>11675.893750000001</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
-    </row>
-    <row r="45" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
+    </row>
+    <row r="45" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
         <v>4</v>
       </c>
       <c r="B45" s="10">
         <f>0.2*B43</f>
-        <v>3297</v>
+        <v>4082</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11">
         <f t="shared" ref="D45:J45" si="2">0.2*D43</f>
-        <v>3328.400000000001</v>
+        <v>4082</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="12">
         <f t="shared" si="2"/>
-        <v>7439.4450000000015</v>
+        <v>7536</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="12">
@@ -2114,37 +2075,37 @@
         <v>2335.1787500000005</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
-    </row>
-    <row r="47" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A47" s="37" t="s">
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
+    </row>
+    <row r="47" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
         <f>1000*B31/(B43*B13*B37)</f>
-        <v>1.8677266414443756</v>
+        <v>1.3028372900984366</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11">
         <f>1000*D31/(D43*D13*D37)</f>
-        <v>2.2162735058412761</v>
+        <v>1.5771188248560024</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="12">
         <f>1000*F31/(F43*F13*F37)</f>
-        <v>7.9366293651016715</v>
+        <v>7.8349413013613081</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="12">
@@ -2163,15 +2124,15 @@
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
-        <v>1.8677266414443754</v>
+        <v>1.3028372900984369</v>
       </c>
       <c r="Q47">
         <f>(1.2*1000*D27*D25*D7*(1-D21))/(D13*D15*D23*(D9*D9-D11*D11)*(1-0.5*D21)*D17)</f>
-        <v>2.2162735058412766</v>
+        <v>1.5771188248560022</v>
       </c>
       <c r="S47">
         <f>(1.2*1000*F27*F25*F7*(1-F21))/(F13*F15*F23*(F9*F9-F11*F11)*(1-0.5*F21)*F17)</f>
-        <v>7.9366293651016733</v>
+        <v>7.8349413013613098</v>
       </c>
       <c r="U47">
         <f>(1.2*1000*H27*H25*H7*(1-H21))/(H13*H15*H23*(H9*H9-H11*H11)*(1-0.5*H21)*H17)</f>
@@ -2186,14 +2147,14 @@
         <v>6.9031399799581443</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A48" s="38"/>
+    <row r="48" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="18">
@@ -2212,23 +2173,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B49" s="20">
         <f>B43/(2*B23*B37*B35*(1-B19))</f>
-        <v>3.0999416824609995</v>
+        <v>2.8626576772509802</v>
       </c>
       <c r="C49" s="21"/>
       <c r="D49" s="21">
         <f>D43/(2*D23*D37*D35*(1-D19))</f>
-        <v>3.06460731907895</v>
+        <v>2.8626576772509802</v>
       </c>
       <c r="E49" s="21"/>
       <c r="F49" s="22">
         <f>F43/(2*F23*F37*F35*(1-F19))</f>
-        <v>3.1141868512110733</v>
+        <v>3.154605230729798</v>
       </c>
       <c r="G49" s="21"/>
       <c r="H49" s="22">
@@ -2247,15 +2208,15 @@
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
-        <v>3.0999416824609995</v>
+        <v>2.8626576772509789</v>
       </c>
       <c r="Q49">
         <f>((D9*D9-D11*D11)*D15*((1-D21)^2))/(1.2*2*(1-0.5*D21)*D17*D17*D21*(1-D19))</f>
-        <v>3.0646073190789473</v>
+        <v>2.8626576772509789</v>
       </c>
       <c r="S49">
         <f>((F9*F9-F11*F11)*F15*((1-F21)^2))/(1.2*2*(1-0.5*F21)*F17*F17*F21*(1-F19))</f>
-        <v>3.114186851211072</v>
+        <v>3.1546052307297976</v>
       </c>
       <c r="U49">
         <f>((H9*H9-H11*H11)*H15*((1-H21)^2))/(1.2*2*(1-0.5*H21)*H17*H17*H21*(1-H19))</f>
@@ -2272,12 +2233,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2294,6 +2249,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826D98A6-4617-4AC8-8F57-22263B3A22F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23258" windowHeight="12578"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -23,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -309,7 +312,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -730,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -790,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -817,9 +820,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -857,9 +860,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -894,7 +897,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -929,7 +932,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1102,33 +1105,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:Y49"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="116.796875" customWidth="1"/>
+    <col min="1" max="1" width="116.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14.46484375" customWidth="1"/>
-    <col min="6" max="6" width="17.46484375" customWidth="1"/>
-    <col min="8" max="8" width="13.53125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="12" max="12" width="14.46484375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-    </row>
-    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1139,7 +1142,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="25.15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
         <v>13</v>
@@ -1165,7 +1168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
         <v>8</v>
       </c>
@@ -1198,21 +1201,21 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
-    </row>
-    <row r="9" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
+    </row>
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
@@ -1237,27 +1240,27 @@
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
         <v>3</v>
       </c>
@@ -1282,24 +1285,24 @@
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9">
-        <v>22.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
-    </row>
-    <row r="13" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
+    </row>
+    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>21</v>
       </c>
@@ -1331,21 +1334,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
-    </row>
-    <row r="15" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
+    </row>
+    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
         <v>20</v>
       </c>
@@ -1378,21 +1381,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
-    </row>
-    <row r="17" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
+    </row>
+    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
@@ -1423,21 +1426,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
-    </row>
-    <row r="19" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
+    </row>
+    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>26</v>
       </c>
@@ -1468,21 +1471,21 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
-    </row>
-    <row r="21" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
+    </row>
+    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
@@ -1507,27 +1510,27 @@
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="32">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
-    </row>
-    <row r="23" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
+    </row>
+    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
@@ -1555,21 +1558,21 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>23</v>
       </c>
@@ -1601,21 +1604,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
-    </row>
-    <row r="27" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
+    </row>
+    <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
         <v>27</v>
       </c>
@@ -1643,21 +1646,21 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
-    </row>
-    <row r="29" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
         <v>7</v>
       </c>
@@ -1691,21 +1694,21 @@
         <v>990</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
-    </row>
-    <row r="31" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
+    </row>
+    <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
         <v>11</v>
       </c>
@@ -1739,21 +1742,21 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
-    </row>
-    <row r="33" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
+    </row>
+    <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
         <v>6</v>
       </c>
@@ -1784,24 +1787,24 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11">
         <f>L17/(1-L21)</f>
-        <v>88.888888888888886</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>90.909090909090907</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
-    </row>
-    <row r="35" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
+    </row>
+    <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
         <v>0</v>
       </c>
@@ -1832,24 +1835,24 @@
       <c r="K35" s="10"/>
       <c r="L35" s="10">
         <f>L33-L17</f>
-        <v>8.8888888888888857</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
+        <v>10.909090909090907</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-    </row>
-    <row r="37" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+    </row>
+    <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
         <v>9</v>
       </c>
@@ -1880,24 +1883,24 @@
       <c r="K37" s="13"/>
       <c r="L37" s="13">
         <f>(L17+L33)/2</f>
-        <v>84.444444444444443</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>85.454545454545453</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
-    </row>
-    <row r="39" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
+    </row>
+    <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
         <v>19</v>
       </c>
@@ -1928,24 +1931,24 @@
       <c r="K39" s="13"/>
       <c r="L39" s="13">
         <f>L23*(L9*L9-L11*L11)</f>
-        <v>9340.7150000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>11052.800000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
-    </row>
-    <row r="41" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
+    </row>
+    <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
         <v>10</v>
       </c>
@@ -1976,24 +1979,24 @@
       <c r="K41" s="13"/>
       <c r="L41" s="13">
         <f>L15*L39</f>
-        <v>14011.0725</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>16579.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
-    </row>
-    <row r="43" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
+    </row>
+    <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
         <v>5</v>
       </c>
@@ -2024,24 +2027,24 @@
       <c r="K43" s="13"/>
       <c r="L43" s="13">
         <f>L41/1.2</f>
-        <v>11675.893750000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>13816.000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
-    </row>
-    <row r="45" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
+    </row>
+    <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
         <v>4</v>
       </c>
@@ -2072,25 +2075,25 @@
       <c r="K45" s="13"/>
       <c r="L45" s="13">
         <f>0.2*L43</f>
-        <v>2335.1787500000005</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+        <v>2763.2000000000007</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
-    </row>
-    <row r="47" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A47" s="41" t="s">
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
+    </row>
+    <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2120,7 +2123,7 @@
       <c r="K47" s="13"/>
       <c r="L47" s="13">
         <f>1000*L31/(L43*L13*L37)</f>
-        <v>6.9031399799581434</v>
+        <v>5.7648817590459407</v>
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
@@ -2144,11 +2147,11 @@
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
-        <v>6.9031399799581443</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
+        <v>5.7648817590459416</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2170,10 +2173,10 @@
       </c>
       <c r="K48" s="19"/>
       <c r="L48" s="19">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
         <v>24</v>
       </c>
@@ -2204,7 +2207,7 @@
       <c r="K49" s="23"/>
       <c r="L49" s="23">
         <f>L43/(2*L23*L37*L35*(1-L19))</f>
-        <v>3.0961496453536195</v>
+        <v>2.9499113475177317</v>
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
@@ -2228,11 +2231,17 @@
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
-        <v>3.096149645353619</v>
+        <v>2.9499113475177303</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2249,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826D98A6-4617-4AC8-8F57-22263B3A22F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -312,7 +311,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -733,6 +732,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,15 +792,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,9 +799,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -820,9 +819,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -860,9 +859,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -897,7 +896,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -932,7 +931,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1105,33 +1104,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:Y49"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="116.85546875" customWidth="1"/>
+    <col min="1" max="1" width="116.86328125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.3984375" customWidth="1"/>
+    <col min="6" max="6" width="17.3984375" customWidth="1"/>
+    <col min="8" max="8" width="13.59765625" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="14.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-    </row>
-    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.5">
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+    </row>
+    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1142,7 +1141,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="26.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="25.15" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
         <v>13</v>
@@ -1168,7 +1167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A7" s="24" t="s">
         <v>8</v>
       </c>
@@ -1201,21 +1200,21 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
-    </row>
-    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
+    </row>
+    <row r="9" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
@@ -1243,24 +1242,24 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A11" s="24" t="s">
         <v>3</v>
       </c>
@@ -1288,21 +1287,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
-    </row>
-    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
+    </row>
+    <row r="13" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
         <v>21</v>
       </c>
@@ -1334,21 +1333,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
-    </row>
-    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
+    </row>
+    <row r="15" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
         <v>20</v>
       </c>
@@ -1381,21 +1380,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
-    </row>
-    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
+    </row>
+    <row r="17" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
@@ -1420,27 +1419,27 @@
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
-    </row>
-    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
+    </row>
+    <row r="19" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
         <v>26</v>
       </c>
@@ -1471,21 +1470,21 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
-    </row>
-    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
+    </row>
+    <row r="21" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
@@ -1516,21 +1515,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
-    </row>
-    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
+    </row>
+    <row r="23" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
@@ -1558,21 +1557,21 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
-    </row>
-    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
+    </row>
+    <row r="25" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
         <v>23</v>
       </c>
@@ -1604,21 +1603,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
-    </row>
-    <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
+    </row>
+    <row r="27" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
         <v>27</v>
       </c>
@@ -1646,21 +1645,21 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
-    </row>
-    <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
+    </row>
+    <row r="29" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A29" s="27" t="s">
         <v>7</v>
       </c>
@@ -1694,21 +1693,21 @@
         <v>990</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
-    </row>
-    <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
+    </row>
+    <row r="31" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A31" s="27" t="s">
         <v>11</v>
       </c>
@@ -1742,21 +1741,21 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
-    </row>
-    <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
+    </row>
+    <row r="33" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A33" s="27" t="s">
         <v>6</v>
       </c>
@@ -1787,24 +1786,24 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11">
         <f>L17/(1-L21)</f>
-        <v>90.909090909090907</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+        <v>102.27272727272727</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
-    </row>
-    <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
+    </row>
+    <row r="35" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A35" s="27" t="s">
         <v>0</v>
       </c>
@@ -1835,24 +1834,24 @@
       <c r="K35" s="10"/>
       <c r="L35" s="10">
         <f>L33-L17</f>
-        <v>10.909090909090907</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+        <v>12.272727272727266</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
-    </row>
-    <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+    </row>
+    <row r="37" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A37" s="27" t="s">
         <v>9</v>
       </c>
@@ -1883,24 +1882,24 @@
       <c r="K37" s="13"/>
       <c r="L37" s="13">
         <f>(L17+L33)/2</f>
-        <v>85.454545454545453</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+        <v>96.136363636363626</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
-    </row>
-    <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
+    </row>
+    <row r="39" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A39" s="27" t="s">
         <v>19</v>
       </c>
@@ -1934,21 +1933,21 @@
         <v>11052.800000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
-    </row>
-    <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
+    </row>
+    <row r="41" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
         <v>10</v>
       </c>
@@ -1982,21 +1981,21 @@
         <v>16579.2</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
-    </row>
-    <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
+    </row>
+    <row r="43" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
         <v>5</v>
       </c>
@@ -2030,21 +2029,21 @@
         <v>13816.000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
-    </row>
-    <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
+    </row>
+    <row r="45" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
         <v>4</v>
       </c>
@@ -2078,22 +2077,22 @@
         <v>2763.2000000000007</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
-    </row>
-    <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
+    </row>
+    <row r="47" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2123,7 +2122,7 @@
       <c r="K47" s="13"/>
       <c r="L47" s="13">
         <f>1000*L31/(L43*L13*L37)</f>
-        <v>5.7648817590459407</v>
+        <v>5.1243393413741698</v>
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
@@ -2147,11 +2146,11 @@
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
-        <v>5.7648817590459416</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
+        <v>5.1243393413741698</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2176,7 +2175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="30" t="s">
         <v>24</v>
       </c>
@@ -2207,7 +2206,7 @@
       <c r="K49" s="23"/>
       <c r="L49" s="23">
         <f>L43/(2*L23*L37*L35*(1-L19))</f>
-        <v>2.9499113475177317</v>
+        <v>2.3307941511251218</v>
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
@@ -2231,17 +2230,11 @@
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
-        <v>2.9499113475177303</v>
+        <v>2.3307941511251205</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2258,6 +2251,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -732,18 +732,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -792,6 +780,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -799,6 +796,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1119,16 +1119,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
@@ -1202,17 +1202,17 @@
     </row>
     <row r="8" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
@@ -1244,17 +1244,17 @@
     </row>
     <row r="10" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9">
@@ -1289,17 +1289,17 @@
     </row>
     <row r="12" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
@@ -1335,17 +1335,17 @@
     </row>
     <row r="14" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
@@ -1382,17 +1382,17 @@
     </row>
     <row r="16" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
@@ -1427,17 +1427,17 @@
     </row>
     <row r="18" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
@@ -1472,17 +1472,17 @@
     </row>
     <row r="20" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="I21" s="32"/>
       <c r="J21" s="32">
-        <v>0.1</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="32">
@@ -1517,17 +1517,17 @@
     </row>
     <row r="22" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
@@ -1559,17 +1559,17 @@
     </row>
     <row r="24" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
@@ -1605,17 +1605,17 @@
     </row>
     <row r="26" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
@@ -1647,17 +1647,17 @@
     </row>
     <row r="28" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A29" s="27" t="s">
@@ -1695,17 +1695,17 @@
     </row>
     <row r="30" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
     </row>
     <row r="31" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A31" s="27" t="s">
@@ -1743,17 +1743,17 @@
     </row>
     <row r="32" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
     </row>
     <row r="33" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A33" s="27" t="s">
@@ -1781,7 +1781,7 @@
       <c r="I33" s="11"/>
       <c r="J33" s="11">
         <f>J17/(1-J21)</f>
-        <v>81.111111111111114</v>
+        <v>80.924855491329481</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="11">
@@ -1791,17 +1791,17 @@
     </row>
     <row r="34" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
     </row>
     <row r="35" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A35" s="27" t="s">
@@ -1829,7 +1829,7 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10">
         <f t="shared" si="0"/>
-        <v>8.1111111111111143</v>
+        <v>10.924855491329481</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10">
@@ -1839,17 +1839,17 @@
     </row>
     <row r="36" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
     </row>
     <row r="37" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A37" s="27" t="s">
@@ -1877,7 +1877,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="13">
         <f>(J17+J33)/2</f>
-        <v>77.055555555555557</v>
+        <v>75.462427745664741</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13">
@@ -1887,17 +1887,17 @@
     </row>
     <row r="38" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A39" s="27" t="s">
@@ -1925,7 +1925,7 @@
       <c r="I39" s="12"/>
       <c r="J39" s="13">
         <f>J23*(J9*J9-J11*J11)</f>
-        <v>7908.875</v>
+        <v>7689.8600000000006</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13">
@@ -1935,17 +1935,17 @@
     </row>
     <row r="40" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
@@ -1973,7 +1973,7 @@
       <c r="I41" s="12"/>
       <c r="J41" s="13">
         <f>J15*J39</f>
-        <v>11863.3125</v>
+        <v>11534.79</v>
       </c>
       <c r="K41" s="13"/>
       <c r="L41" s="13">
@@ -1983,17 +1983,17 @@
     </row>
     <row r="42" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
@@ -2021,7 +2021,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="13">
         <f t="shared" si="1"/>
-        <v>9886.09375</v>
+        <v>9612.3250000000007</v>
       </c>
       <c r="K43" s="13"/>
       <c r="L43" s="13">
@@ -2031,17 +2031,17 @@
     </row>
     <row r="44" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
@@ -2069,7 +2069,7 @@
       <c r="I45" s="12"/>
       <c r="J45" s="13">
         <f t="shared" si="2"/>
-        <v>1977.21875</v>
+        <v>1922.4650000000001</v>
       </c>
       <c r="K45" s="13"/>
       <c r="L45" s="13">
@@ -2079,20 +2079,20 @@
     </row>
     <row r="46" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2117,7 +2117,7 @@
       <c r="I47" s="12"/>
       <c r="J47" s="13">
         <f>1000*J31/(J43*J13*J37)</f>
-        <v>3.7412452587618859</v>
+        <v>3.9290326770258641</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
-        <v>3.7412452587618863</v>
+        <v>3.929032677025865</v>
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
@@ -2150,7 +2150,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="I49" s="22"/>
       <c r="J49" s="23">
         <f>J43/(2*J23*J37*J35*(1-J19))</f>
-        <v>3.1484064046281013</v>
+        <v>2.3207712802875093</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
-        <v>3.1484064046281026</v>
+        <v>2.3207712802875098</v>
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
@@ -2235,6 +2235,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2251,12 +2257,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -732,6 +732,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -780,15 +792,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -796,9 +799,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1119,16 +1119,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="1"/>
@@ -1202,17 +1202,17 @@
     </row>
     <row r="8" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
@@ -1244,17 +1244,17 @@
     </row>
     <row r="10" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1289,17 +1289,17 @@
     </row>
     <row r="12" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A13" s="24" t="s">
@@ -1335,17 +1335,17 @@
     </row>
     <row r="14" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A15" s="24" t="s">
@@ -1382,17 +1382,17 @@
     </row>
     <row r="16" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
@@ -1427,17 +1427,17 @@
     </row>
     <row r="18" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A19" s="24" t="s">
@@ -1472,17 +1472,17 @@
     </row>
     <row r="20" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="I21" s="32"/>
       <c r="J21" s="32">
-        <v>0.13500000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="32">
@@ -1517,17 +1517,17 @@
     </row>
     <row r="22" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A23" s="24" t="s">
@@ -1559,17 +1559,17 @@
     </row>
     <row r="24" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A25" s="24" t="s">
@@ -1605,17 +1605,17 @@
     </row>
     <row r="26" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A27" s="24" t="s">
@@ -1647,17 +1647,17 @@
     </row>
     <row r="28" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A29" s="27" t="s">
@@ -1695,17 +1695,17 @@
     </row>
     <row r="30" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A31" s="27" t="s">
@@ -1743,17 +1743,17 @@
     </row>
     <row r="32" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A33" s="27" t="s">
@@ -1781,7 +1781,7 @@
       <c r="I33" s="11"/>
       <c r="J33" s="11">
         <f>J17/(1-J21)</f>
-        <v>80.924855491329481</v>
+        <v>90.909090909090907</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="11">
@@ -1791,17 +1791,17 @@
     </row>
     <row r="34" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A35" s="27" t="s">
@@ -1829,7 +1829,7 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10">
         <f t="shared" si="0"/>
-        <v>10.924855491329481</v>
+        <v>10.909090909090907</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10">
@@ -1839,17 +1839,17 @@
     </row>
     <row r="36" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A37" s="27" t="s">
@@ -1877,7 +1877,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="13">
         <f>(J17+J33)/2</f>
-        <v>75.462427745664741</v>
+        <v>85.454545454545453</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13">
@@ -1887,17 +1887,17 @@
     </row>
     <row r="38" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A39" s="27" t="s">
@@ -1935,17 +1935,17 @@
     </row>
     <row r="40" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A41" s="27" t="s">
@@ -1983,17 +1983,17 @@
     </row>
     <row r="42" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A43" s="27" t="s">
@@ -2031,17 +2031,17 @@
     </row>
     <row r="44" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A45" s="27" t="s">
@@ -2079,20 +2079,20 @@
     </row>
     <row r="46" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2117,7 +2117,7 @@
       <c r="I47" s="12"/>
       <c r="J47" s="13">
         <f>1000*J31/(J43*J13*J37)</f>
-        <v>3.9290326770258641</v>
+        <v>3.4696146696857664</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
-        <v>3.929032677025865</v>
+        <v>3.4696146696857664</v>
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
@@ -2150,7 +2150,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A48" s="38"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2201,7 +2201,7 @@
       <c r="I49" s="22"/>
       <c r="J49" s="23">
         <f>J43/(2*J23*J37*J35*(1-J19))</f>
-        <v>2.3207712802875093</v>
+        <v>2.0523672983156036</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
-        <v>2.3207712802875098</v>
+        <v>2.0523672983156023</v>
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
@@ -2235,12 +2235,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2257,6 +2251,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4347B81-3386-43D9-8963-2AE936BC1345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -311,7 +312,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -732,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -792,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -799,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -819,9 +820,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -859,9 +860,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -896,7 +897,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -931,7 +932,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1104,33 +1105,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A4:Y49"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="116.86328125" customWidth="1"/>
+    <col min="1" max="1" width="116.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14.3984375" customWidth="1"/>
-    <col min="6" max="6" width="17.3984375" customWidth="1"/>
-    <col min="8" max="8" width="13.59765625" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.42578125" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="12" max="12" width="14.3984375" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-    </row>
-    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -1141,7 +1142,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:14" ht="25.15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="26.25" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
         <v>13</v>
@@ -1167,7 +1168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
         <v>8</v>
       </c>
@@ -1200,21 +1201,21 @@
         <v>750</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
-    </row>
-    <row r="9" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
+    </row>
+    <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
@@ -1242,24 +1243,24 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
         <v>3</v>
       </c>
@@ -1287,21 +1288,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
-    </row>
-    <row r="13" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
+    </row>
+    <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>21</v>
       </c>
@@ -1333,21 +1334,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
-    </row>
-    <row r="15" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
+    </row>
+    <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
         <v>20</v>
       </c>
@@ -1380,21 +1381,21 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
-    </row>
-    <row r="17" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
+    </row>
+    <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
@@ -1407,7 +1408,7 @@
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9">
@@ -1425,21 +1426,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
-    </row>
-    <row r="19" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
+    </row>
+    <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>26</v>
       </c>
@@ -1470,21 +1471,21 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
-    </row>
-    <row r="21" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
+    </row>
+    <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
@@ -1515,21 +1516,21 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
-    </row>
-    <row r="23" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
+    </row>
+    <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>18</v>
       </c>
@@ -1557,21 +1558,21 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
+    </row>
+    <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>23</v>
       </c>
@@ -1603,21 +1604,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
-    </row>
-    <row r="27" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
+    </row>
+    <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
         <v>27</v>
       </c>
@@ -1645,21 +1646,21 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
-    </row>
-    <row r="29" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
+    </row>
+    <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
         <v>7</v>
       </c>
@@ -1693,21 +1694,21 @@
         <v>990</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
-    </row>
-    <row r="31" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
+    </row>
+    <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
         <v>11</v>
       </c>
@@ -1741,21 +1742,21 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
-    </row>
-    <row r="33" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
+    </row>
+    <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
         <v>6</v>
       </c>
@@ -1771,7 +1772,7 @@
       <c r="E33" s="11"/>
       <c r="F33" s="11">
         <f>F17/(1-F21)</f>
-        <v>127.5</v>
+        <v>162.5</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="11">
@@ -1789,21 +1790,21 @@
         <v>102.27272727272727</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
-    </row>
-    <row r="35" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
+    </row>
+    <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
         <v>0</v>
       </c>
@@ -1819,7 +1820,7 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10">
         <f t="shared" si="0"/>
-        <v>25.5</v>
+        <v>32.5</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="10">
@@ -1837,21 +1838,21 @@
         <v>12.272727272727266</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="17.25" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
-    </row>
-    <row r="37" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+    </row>
+    <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
         <v>9</v>
       </c>
@@ -1867,7 +1868,7 @@
       <c r="E37" s="11"/>
       <c r="F37" s="12">
         <f>(F17+F33)/2</f>
-        <v>114.75</v>
+        <v>146.25</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="12">
@@ -1885,21 +1886,21 @@
         <v>96.136363636363626</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
-    </row>
-    <row r="39" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
+    </row>
+    <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
         <v>19</v>
       </c>
@@ -1933,21 +1934,21 @@
         <v>11052.800000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
-    </row>
-    <row r="41" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
+    </row>
+    <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
         <v>10</v>
       </c>
@@ -1981,21 +1982,21 @@
         <v>16579.2</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
-    </row>
-    <row r="43" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
+    </row>
+    <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
         <v>5</v>
       </c>
@@ -2029,21 +2030,21 @@
         <v>13816.000000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
-    </row>
-    <row r="45" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
+    </row>
+    <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
         <v>4</v>
       </c>
@@ -2077,22 +2078,22 @@
         <v>2763.2000000000007</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
-    </row>
-    <row r="47" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A47" s="41" t="s">
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
+    </row>
+    <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2107,7 +2108,7 @@
       <c r="E47" s="11"/>
       <c r="F47" s="12">
         <f>1000*F31/(F43*F13*F37)</f>
-        <v>7.8349413013613081</v>
+        <v>6.147415482606565</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="12">
@@ -2134,7 +2135,7 @@
       </c>
       <c r="S47">
         <f>(1.2*1000*F27*F25*F7*(1-F21))/(F13*F15*F23*(F9*F9-F11*F11)*(1-0.5*F21)*F17)</f>
-        <v>7.8349413013613098</v>
+        <v>6.1474154826065668</v>
       </c>
       <c r="U47">
         <f>(1.2*1000*H27*H25*H7*(1-H21))/(H13*H15*H23*(H9*H9-H11*H11)*(1-0.5*H21)*H17)</f>
@@ -2149,8 +2150,8 @@
         <v>5.1243393413741698</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="17.649999999999999" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
+    <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2175,7 +2176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:25" ht="18.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
         <v>24</v>
       </c>
@@ -2191,7 +2192,7 @@
       <c r="E49" s="21"/>
       <c r="F49" s="22">
         <f>F43/(2*F23*F37*F35*(1-F19))</f>
-        <v>3.154605230729798</v>
+        <v>1.9420421787285691</v>
       </c>
       <c r="G49" s="21"/>
       <c r="H49" s="22">
@@ -2218,7 +2219,7 @@
       </c>
       <c r="S49">
         <f>((F9*F9-F11*F11)*F15*((1-F21)^2))/(1.2*2*(1-0.5*F21)*F17*F17*F21*(1-F19))</f>
-        <v>3.1546052307297976</v>
+        <v>1.9420421787285695</v>
       </c>
       <c r="U49">
         <f>((H9*H9-H11*H11)*H15*((1-H21)^2))/(1.2*2*(1-0.5*H21)*H17*H17*H21*(1-H19))</f>
@@ -2235,6 +2236,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2251,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4347B81-3386-43D9-8963-2AE936BC1345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEE5486-F09E-4D96-ADE8-A21AA5A717BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -733,6 +733,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,15 +793,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,9 +800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9">
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,32 +1383,32 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="31">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="9">
-        <v>110</v>
+      <c r="D17" s="31">
+        <v>120</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G17" s="9"/>
       <c r="H17" s="9">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="32">
-        <v>0.2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="32">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I21" s="32"/>
       <c r="J21" s="32">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="32">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1762,17 +1762,17 @@
       </c>
       <c r="B33" s="11">
         <f>B17/(1-B21)</f>
-        <v>122.22222222222221</v>
+        <v>133.33333333333334</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11">
         <f>D17/(1-D21)</f>
-        <v>122.22222222222221</v>
+        <v>133.33333333333334</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="11">
         <f>F17/(1-F21)</f>
-        <v>162.5</v>
+        <v>162.7906976744186</v>
       </c>
       <c r="G33" s="11"/>
       <c r="H33" s="11">
@@ -1782,7 +1782,7 @@
       <c r="I33" s="11"/>
       <c r="J33" s="11">
         <f>J17/(1-J21)</f>
-        <v>90.909090909090907</v>
+        <v>86.206896551724142</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="11">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1810,17 +1810,17 @@
       </c>
       <c r="B35" s="10">
         <f>B33-B17</f>
-        <v>12.222222222222214</v>
+        <v>13.333333333333343</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10">
         <f t="shared" ref="D35:J35" si="0">D33-D17</f>
-        <v>12.222222222222214</v>
+        <v>13.333333333333343</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="10">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>22.790697674418595</v>
       </c>
       <c r="G35" s="10"/>
       <c r="H35" s="10">
@@ -1830,7 +1830,7 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10">
         <f t="shared" si="0"/>
-        <v>10.909090909090907</v>
+        <v>11.206896551724142</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1858,17 +1858,17 @@
       </c>
       <c r="B37" s="10">
         <f>(B17+B33)/2</f>
-        <v>116.11111111111111</v>
+        <v>126.66666666666667</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11">
         <f>(D17+D33)/2</f>
-        <v>116.11111111111111</v>
+        <v>126.66666666666667</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="12">
         <f>(F17+F33)/2</f>
-        <v>146.25</v>
+        <v>151.3953488372093</v>
       </c>
       <c r="G37" s="11"/>
       <c r="H37" s="12">
@@ -1878,7 +1878,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="13">
         <f>(J17+J33)/2</f>
-        <v>85.454545454545453</v>
+        <v>80.603448275862064</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1916,7 +1916,7 @@
       <c r="E39" s="11"/>
       <c r="F39" s="12">
         <f>F23*(F9*F9-F11*F11)</f>
-        <v>30144</v>
+        <v>23157.5</v>
       </c>
       <c r="G39" s="11"/>
       <c r="H39" s="12">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1964,7 +1964,7 @@
       <c r="E41" s="11"/>
       <c r="F41" s="12">
         <f>F15*F39</f>
-        <v>45216</v>
+        <v>34736.25</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="12">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2012,7 +2012,7 @@
       <c r="E43" s="11"/>
       <c r="F43" s="12">
         <f t="shared" si="1"/>
-        <v>37680</v>
+        <v>28946.875</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="12">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2060,7 +2060,7 @@
       <c r="E45" s="11"/>
       <c r="F45" s="12">
         <f t="shared" si="2"/>
-        <v>7536</v>
+        <v>5789.375</v>
       </c>
       <c r="G45" s="11"/>
       <c r="H45" s="12">
@@ -2080,35 +2080,35 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
         <f>1000*B31/(B43*B13*B37)</f>
-        <v>1.3028372900984366</v>
+        <v>1.1942675159235669</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11">
         <f>1000*D31/(D43*D13*D37)</f>
-        <v>1.5771188248560024</v>
+        <v>1.4456922561180021</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="12">
         <f>1000*F31/(F43*F13*F37)</f>
-        <v>6.147415482606565</v>
+        <v>7.7301000810419129</v>
       </c>
       <c r="G47" s="11"/>
       <c r="H47" s="12">
@@ -2118,7 +2118,7 @@
       <c r="I47" s="12"/>
       <c r="J47" s="13">
         <f>1000*J31/(J43*J13*J37)</f>
-        <v>3.4696146696857664</v>
+        <v>3.9849685517525262</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13">
@@ -2127,15 +2127,15 @@
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
-        <v>1.3028372900984369</v>
+        <v>1.1942675159235672</v>
       </c>
       <c r="Q47">
         <f>(1.2*1000*D27*D25*D7*(1-D21))/(D13*D15*D23*(D9*D9-D11*D11)*(1-0.5*D21)*D17)</f>
-        <v>1.5771188248560022</v>
+        <v>1.4456922561180023</v>
       </c>
       <c r="S47">
         <f>(1.2*1000*F27*F25*F7*(1-F21))/(F13*F15*F23*(F9*F9-F11*F11)*(1-0.5*F21)*F17)</f>
-        <v>6.1474154826065668</v>
+        <v>7.7301000810419156</v>
       </c>
       <c r="U47">
         <f>(1.2*1000*H27*H25*H7*(1-H21))/(H13*H15*H23*(H9*H9-H11*H11)*(1-0.5*H21)*H17)</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
-        <v>3.4696146696857664</v>
+        <v>3.9849685517525266</v>
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="B49" s="20">
         <f>B43/(2*B23*B37*B35*(1-B19))</f>
-        <v>2.8626576772509802</v>
+        <v>2.4054276315789456</v>
       </c>
       <c r="C49" s="21"/>
       <c r="D49" s="21">
         <f>D43/(2*D23*D37*D35*(1-D19))</f>
-        <v>2.8626576772509802</v>
+        <v>2.4054276315789456</v>
       </c>
       <c r="E49" s="21"/>
       <c r="F49" s="22">
         <f>F43/(2*F23*F37*F35*(1-F19))</f>
-        <v>1.9420421787285691</v>
+        <v>2.0552210160916555</v>
       </c>
       <c r="G49" s="21"/>
       <c r="H49" s="22">
@@ -2202,7 +2202,7 @@
       <c r="I49" s="22"/>
       <c r="J49" s="23">
         <f>J43/(2*J23*J37*J35*(1-J19))</f>
-        <v>2.0523672983156036</v>
+        <v>2.1180676676264905</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23">
@@ -2211,15 +2211,15 @@
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
-        <v>2.8626576772509789</v>
+        <v>2.4054276315789478</v>
       </c>
       <c r="Q49">
         <f>((D9*D9-D11*D11)*D15*((1-D21)^2))/(1.2*2*(1-0.5*D21)*D17*D17*D21*(1-D19))</f>
-        <v>2.8626576772509789</v>
+        <v>2.4054276315789478</v>
       </c>
       <c r="S49">
         <f>((F9*F9-F11*F11)*F15*((1-F21)^2))/(1.2*2*(1-0.5*F21)*F17*F17*F21*(1-F19))</f>
-        <v>1.9420421787285695</v>
+        <v>2.0552210160916542</v>
       </c>
       <c r="U49">
         <f>((H9*H9-H11*H11)*H15*((1-H21)^2))/(1.2*2*(1-0.5*H21)*H17*H17*H21*(1-H19))</f>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
-        <v>2.0523672983156023</v>
+        <v>2.1180676676264913</v>
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
@@ -2236,12 +2236,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2258,6 +2252,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEE5486-F09E-4D96-ADE8-A21AA5A717BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B6F5E4-7225-4A25-BDA5-F96EDD65F5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28020" yWindow="780" windowWidth="25770" windowHeight="14205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -793,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="32">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="I21" s="32"/>
       <c r="J21" s="32">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1777,7 +1777,7 @@
       <c r="G33" s="11"/>
       <c r="H33" s="11">
         <f>H17/(1-H21)</f>
-        <v>88.888888888888886</v>
+        <v>91.428571428571431</v>
       </c>
       <c r="I33" s="11"/>
       <c r="J33" s="11">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1825,7 +1825,7 @@
       <c r="G35" s="10"/>
       <c r="H35" s="10">
         <f t="shared" si="0"/>
-        <v>8.8888888888888857</v>
+        <v>11.428571428571431</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1873,7 +1873,7 @@
       <c r="G37" s="11"/>
       <c r="H37" s="12">
         <f>(H17+H33)/2</f>
-        <v>84.444444444444443</v>
+        <v>85.714285714285722</v>
       </c>
       <c r="I37" s="12"/>
       <c r="J37" s="13">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2080,20 +2080,20 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2113,7 +2113,7 @@
       <c r="G47" s="11"/>
       <c r="H47" s="12">
         <f>1000*H31/(H43*H13*H37)</f>
-        <v>4.8066494448936128</v>
+        <v>4.7354398234877806</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="13">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="U47">
         <f>(1.2*1000*H27*H25*H7*(1-H21))/(H13*H15*H23*(H9*H9-H11*H11)*(1-0.5*H21)*H17)</f>
-        <v>4.8066494448936128</v>
+        <v>4.7354398234877815</v>
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="42"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G48" s="17"/>
       <c r="H48" s="18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I48" s="18"/>
       <c r="J48" s="19">
@@ -2197,7 +2197,7 @@
       <c r="G49" s="21"/>
       <c r="H49" s="22">
         <f>H43/(2*H23*H37*H35*(1-H19))</f>
-        <v>3.1317973889802642</v>
+        <v>2.3997558593749995</v>
       </c>
       <c r="I49" s="22"/>
       <c r="J49" s="23">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="U49">
         <f>((H9*H9-H11*H11)*H15*((1-H21)^2))/(1.2*2*(1-0.5*H21)*H17*H17*H21*(1-H19))</f>
-        <v>3.1317973889802637</v>
+        <v>2.3997558593749999</v>
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
@@ -2236,6 +2236,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2252,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B6F5E4-7225-4A25-BDA5-F96EDD65F5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34F237A-8314-42FC-9BE3-2B9F982F49EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28020" yWindow="780" windowWidth="25770" windowHeight="14205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27525" yWindow="510" windowWidth="25770" windowHeight="14205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,6 +733,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,15 +793,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,9 +800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9">
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1926,7 +1926,7 @@
       <c r="I39" s="12"/>
       <c r="J39" s="13">
         <f>J23*(J9*J9-J11*J11)</f>
-        <v>7689.8600000000006</v>
+        <v>8101.2000000000007</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1974,7 +1974,7 @@
       <c r="I41" s="12"/>
       <c r="J41" s="13">
         <f>J15*J39</f>
-        <v>11534.79</v>
+        <v>12151.800000000001</v>
       </c>
       <c r="K41" s="13"/>
       <c r="L41" s="13">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2022,7 +2022,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="13">
         <f t="shared" si="1"/>
-        <v>9612.3250000000007</v>
+        <v>10126.500000000002</v>
       </c>
       <c r="K43" s="13"/>
       <c r="L43" s="13">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2070,7 +2070,7 @@
       <c r="I45" s="12"/>
       <c r="J45" s="13">
         <f t="shared" si="2"/>
-        <v>1922.4650000000001</v>
+        <v>2025.3000000000004</v>
       </c>
       <c r="K45" s="13"/>
       <c r="L45" s="13">
@@ -2080,20 +2080,20 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2118,7 +2118,7 @@
       <c r="I47" s="12"/>
       <c r="J47" s="13">
         <f>1000*J31/(J43*J13*J37)</f>
-        <v>3.9849685517525262</v>
+        <v>3.782631001256564</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
-        <v>3.9849685517525266</v>
+        <v>3.7826310012565645</v>
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2202,7 +2202,7 @@
       <c r="I49" s="22"/>
       <c r="J49" s="23">
         <f>J43/(2*J23*J37*J35*(1-J19))</f>
-        <v>2.1180676676264905</v>
+        <v>2.2313656931303982</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
-        <v>2.1180676676264913</v>
+        <v>2.2313656931303991</v>
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
@@ -2236,12 +2236,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2258,6 +2252,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34F237A-8314-42FC-9BE3-2B9F982F49EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ED1C65-6DDA-4663-AE69-4719CB3C2FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27525" yWindow="510" windowWidth="25770" windowHeight="14205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21135" yWindow="0" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -793,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,24 +1203,24 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="31">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="31">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1265,11 +1265,11 @@
         <v>3</v>
       </c>
       <c r="B11" s="31">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="31">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9">
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,24 +1383,24 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="31">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="31">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="9">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,24 +1473,24 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="32">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="C21" s="32"/>
       <c r="D21" s="32">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I21" s="32"/>
       <c r="J21" s="32">
-        <v>0.13</v>
+        <v>0.115</v>
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="32">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9">
-        <v>0.46</v>
+        <v>0.78</v>
       </c>
       <c r="E27" s="9"/>
       <c r="F27" s="9">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9">
-        <v>0.38</v>
+        <v>0.61</v>
       </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1671,7 +1671,7 @@
       <c r="C29" s="11"/>
       <c r="D29" s="11">
         <f>D7*D27</f>
-        <v>345</v>
+        <v>585</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="12">
@@ -1686,7 +1686,7 @@
       <c r="I29" s="12"/>
       <c r="J29" s="13">
         <f>J7*J27</f>
-        <v>285</v>
+        <v>457.5</v>
       </c>
       <c r="K29" s="13"/>
       <c r="L29" s="13">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1719,7 +1719,7 @@
       <c r="C31" s="11"/>
       <c r="D31" s="11">
         <f>D29*D25</f>
-        <v>448.5</v>
+        <v>760.5</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="12">
@@ -1734,7 +1734,7 @@
       <c r="I31" s="12"/>
       <c r="J31" s="13">
         <f>J29*J25</f>
-        <v>370.5</v>
+        <v>594.75</v>
       </c>
       <c r="K31" s="13"/>
       <c r="L31" s="13">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B33" s="11">
         <f>B17/(1-B21)</f>
-        <v>133.33333333333334</v>
+        <v>143.67816091954023</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11">
@@ -1782,7 +1782,7 @@
       <c r="I33" s="11"/>
       <c r="J33" s="11">
         <f>J17/(1-J21)</f>
-        <v>86.206896551724142</v>
+        <v>96.045197740112997</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="11">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B35" s="10">
         <f>B33-B17</f>
-        <v>13.333333333333343</v>
+        <v>18.678160919540232</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10">
@@ -1830,7 +1830,7 @@
       <c r="I35" s="10"/>
       <c r="J35" s="10">
         <f t="shared" si="0"/>
-        <v>11.206896551724142</v>
+        <v>11.045197740112997</v>
       </c>
       <c r="K35" s="10"/>
       <c r="L35" s="10">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B37" s="10">
         <f>(B17+B33)/2</f>
-        <v>126.66666666666667</v>
+        <v>134.33908045977012</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11">
@@ -1878,7 +1878,7 @@
       <c r="I37" s="12"/>
       <c r="J37" s="13">
         <f>(J17+J33)/2</f>
-        <v>80.603448275862064</v>
+        <v>90.522598870056498</v>
       </c>
       <c r="K37" s="13"/>
       <c r="L37" s="13">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B39" s="10">
         <f>B23*(B9*B9-B11*B11)</f>
-        <v>16328</v>
+        <v>12952.5</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11">
         <f>D23*(D9*D9-D11*D11)</f>
-        <v>16328</v>
+        <v>12481.5</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="12">
@@ -1926,7 +1926,7 @@
       <c r="I39" s="12"/>
       <c r="J39" s="13">
         <f>J23*(J9*J9-J11*J11)</f>
-        <v>8101.2000000000007</v>
+        <v>12057.6</v>
       </c>
       <c r="K39" s="13"/>
       <c r="L39" s="13">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B41" s="10">
         <f>B15*B39</f>
-        <v>24492</v>
+        <v>19428.75</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11">
         <f>D15*D39</f>
-        <v>24492</v>
+        <v>18722.25</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="12">
@@ -1974,7 +1974,7 @@
       <c r="I41" s="12"/>
       <c r="J41" s="13">
         <f>J15*J39</f>
-        <v>12151.800000000001</v>
+        <v>18086.400000000001</v>
       </c>
       <c r="K41" s="13"/>
       <c r="L41" s="13">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2002,12 +2002,12 @@
       </c>
       <c r="B43" s="10">
         <f>B41/1.2</f>
-        <v>20410</v>
+        <v>16190.625</v>
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11">
         <f t="shared" ref="D43:J43" si="1">D41/1.2</f>
-        <v>20410</v>
+        <v>15601.875</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="12">
@@ -2022,7 +2022,7 @@
       <c r="I43" s="12"/>
       <c r="J43" s="13">
         <f t="shared" si="1"/>
-        <v>10126.500000000002</v>
+        <v>15072.000000000002</v>
       </c>
       <c r="K43" s="13"/>
       <c r="L43" s="13">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="B45" s="10">
         <f>0.2*B43</f>
-        <v>4082</v>
+        <v>3238.125</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11">
         <f t="shared" ref="D45:J45" si="2">0.2*D43</f>
-        <v>4082</v>
+        <v>3120.375</v>
       </c>
       <c r="E45" s="11"/>
       <c r="F45" s="12">
@@ -2070,7 +2070,7 @@
       <c r="I45" s="12"/>
       <c r="J45" s="13">
         <f t="shared" si="2"/>
-        <v>2025.3000000000004</v>
+        <v>3014.4000000000005</v>
       </c>
       <c r="K45" s="13"/>
       <c r="L45" s="13">
@@ -2080,30 +2080,30 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
         <f>1000*B31/(B43*B13*B37)</f>
-        <v>1.1942675159235669</v>
+        <v>1.4195182521079179</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11">
         <f>1000*D31/(D43*D13*D37)</f>
-        <v>1.4456922561180021</v>
+        <v>3.206851403234682</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="12">
@@ -2118,7 +2118,7 @@
       <c r="I47" s="12"/>
       <c r="J47" s="13">
         <f>1000*J31/(J43*J13*J37)</f>
-        <v>3.782631001256564</v>
+        <v>3.6326646296559475</v>
       </c>
       <c r="K47" s="13"/>
       <c r="L47" s="13">
@@ -2127,11 +2127,11 @@
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
-        <v>1.1942675159235672</v>
+        <v>1.4195182521079179</v>
       </c>
       <c r="Q47">
         <f>(1.2*1000*D27*D25*D7*(1-D21))/(D13*D15*D23*(D9*D9-D11*D11)*(1-0.5*D21)*D17)</f>
-        <v>1.4456922561180023</v>
+        <v>3.2068514032346824</v>
       </c>
       <c r="S47">
         <f>(1.2*1000*F27*F25*F7*(1-F21))/(F13*F15*F23*(F9*F9-F11*F11)*(1-0.5*F21)*F17)</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
-        <v>3.7826310012565645</v>
+        <v>3.6326646296559479</v>
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="42"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G48" s="17"/>
       <c r="H48" s="18">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I48" s="18"/>
       <c r="J48" s="19">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="B49" s="20">
         <f>B43/(2*B23*B37*B35*(1-B19))</f>
-        <v>2.4054276315789456</v>
+        <v>1.28433257918552</v>
       </c>
       <c r="C49" s="21"/>
       <c r="D49" s="21">
         <f>D43/(2*D23*D37*D35*(1-D19))</f>
-        <v>2.4054276315789456</v>
+        <v>1.8387643914473673</v>
       </c>
       <c r="E49" s="21"/>
       <c r="F49" s="22">
@@ -2202,7 +2202,7 @@
       <c r="I49" s="22"/>
       <c r="J49" s="23">
         <f>J43/(2*J23*J37*J35*(1-J19))</f>
-        <v>2.2313656931303982</v>
+        <v>3.0004800634018891</v>
       </c>
       <c r="K49" s="23"/>
       <c r="L49" s="23">
@@ -2211,11 +2211,11 @@
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
-        <v>2.4054276315789478</v>
+        <v>1.2843325791855205</v>
       </c>
       <c r="Q49">
         <f>((D9*D9-D11*D11)*D15*((1-D21)^2))/(1.2*2*(1-0.5*D21)*D17*D17*D21*(1-D19))</f>
-        <v>2.4054276315789478</v>
+        <v>1.8387643914473688</v>
       </c>
       <c r="S49">
         <f>((F9*F9-F11*F11)*F15*((1-F21)^2))/(1.2*2*(1-0.5*F21)*F17*F17*F21*(1-F19))</f>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
-        <v>2.2313656931303991</v>
+        <v>3.0004800634018891</v>
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
@@ -2236,6 +2236,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2252,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98ED1C65-6DDA-4663-AE69-4719CB3C2FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7804C7A6-2058-43E0-AF5C-CF03E7B53E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21135" yWindow="0" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22095" yWindow="630" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,6 +733,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,15 +793,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,9 +800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,24 +1203,24 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="31">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="31">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="31">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="31">
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,24 +1383,24 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
       <c r="B17" s="31">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="31">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,24 +1473,24 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="32">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="C21" s="32"/>
       <c r="D21" s="32">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B33" s="11">
         <f>B17/(1-B21)</f>
-        <v>143.67816091954023</v>
+        <v>133.33333333333334</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B35" s="10">
         <f>B33-B17</f>
-        <v>18.678160919540232</v>
+        <v>13.333333333333343</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B37" s="10">
         <f>(B17+B33)/2</f>
-        <v>134.33908045977012</v>
+        <v>126.66666666666667</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B39" s="10">
         <f>B23*(B9*B9-B11*B11)</f>
-        <v>12952.5</v>
+        <v>12481.5</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B41" s="10">
         <f>B15*B39</f>
-        <v>19428.75</v>
+        <v>18722.25</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="B43" s="10">
         <f>B41/1.2</f>
-        <v>16190.625</v>
+        <v>15601.875</v>
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B45" s="10">
         <f>0.2*B43</f>
-        <v>3238.125</v>
+        <v>3120.375</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11">
@@ -2080,25 +2080,25 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
         <f>1000*B31/(B43*B13*B37)</f>
-        <v>1.4195182521079179</v>
+        <v>1.5623122220886914</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
-        <v>1.4195182521079179</v>
+        <v>1.5623122220886916</v>
       </c>
       <c r="Q47">
         <f>(1.2*1000*D27*D25*D7*(1-D21))/(D13*D15*D23*(D9*D9-D11*D11)*(1-0.5*D21)*D17)</f>
@@ -2151,13 +2151,13 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E48" s="17"/>
       <c r="F48" s="18">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B49" s="20">
         <f>B43/(2*B23*B37*B35*(1-B19))</f>
-        <v>1.28433257918552</v>
+        <v>1.8387643914473673</v>
       </c>
       <c r="C49" s="21"/>
       <c r="D49" s="21">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
-        <v>1.2843325791855205</v>
+        <v>1.8387643914473688</v>
       </c>
       <c r="Q49">
         <f>((D9*D9-D11*D11)*D15*((1-D21)^2))/(1.2*2*(1-0.5*D21)*D17*D17*D21*(1-D19))</f>
@@ -2236,12 +2236,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2258,6 +2252,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7804C7A6-2058-43E0-AF5C-CF03E7B53E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96381E0A-97E5-4013-9A2A-1FB25736E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22095" yWindow="630" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -793,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,24 +1473,24 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="32">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="C21" s="32"/>
       <c r="D21" s="32">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B33" s="11">
         <f>B17/(1-B21)</f>
-        <v>133.33333333333334</v>
+        <v>142.85714285714286</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="B35" s="10">
         <f>B33-B17</f>
-        <v>13.333333333333343</v>
+        <v>22.857142857142861</v>
       </c>
       <c r="C35" s="10"/>
       <c r="D35" s="10">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B37" s="10">
         <f>(B17+B33)/2</f>
-        <v>126.66666666666667</v>
+        <v>131.42857142857144</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2080,25 +2080,25 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
         <f>1000*B31/(B43*B13*B37)</f>
-        <v>1.5623122220886914</v>
+        <v>1.5057067067956227</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
-        <v>1.5623122220886916</v>
+        <v>1.5057067067956229</v>
       </c>
       <c r="Q47">
         <f>(1.2*1000*D27*D25*D7*(1-D21))/(D13*D15*D23*(D9*D9-D11*D11)*(1-0.5*D21)*D17)</f>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="42"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="B49" s="20">
         <f>B43/(2*B23*B37*B35*(1-B19))</f>
-        <v>1.8387643914473673</v>
+        <v>1.033749787703804</v>
       </c>
       <c r="C49" s="21"/>
       <c r="D49" s="21">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
-        <v>1.8387643914473688</v>
+        <v>1.033749787703804</v>
       </c>
       <c r="Q49">
         <f>((D9*D9-D11*D11)*D15*((1-D21)^2))/(1.2*2*(1-0.5*D21)*D17*D17*D21*(1-D19))</f>
@@ -2236,6 +2236,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2252,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96381E0A-97E5-4013-9A2A-1FB25736E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12246C15-25A3-4652-9521-0CED60EB5E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -733,6 +733,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,15 +793,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,9 +800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2080,20 +2080,20 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2236,12 +2236,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2258,6 +2252,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12246C15-25A3-4652-9521-0CED60EB5E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67283A3-73B9-4307-B461-5D53218FFA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -793,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1921,7 +1921,7 @@
       <c r="G39" s="11"/>
       <c r="H39" s="12">
         <f>H23*(H9*H9-H11*H11)</f>
-        <v>9448.26</v>
+        <v>11304</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="13">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1969,7 +1969,7 @@
       <c r="G41" s="11"/>
       <c r="H41" s="12">
         <f>H15*H39</f>
-        <v>14172.39</v>
+        <v>16956</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="13">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2017,7 +2017,7 @@
       <c r="G43" s="11"/>
       <c r="H43" s="12">
         <f t="shared" si="1"/>
-        <v>11810.325000000001</v>
+        <v>14130</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="13">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2065,7 +2065,7 @@
       <c r="G45" s="11"/>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>2362.0650000000001</v>
+        <v>2826</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="13">
@@ -2080,20 +2080,20 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2113,7 +2113,7 @@
       <c r="G47" s="11"/>
       <c r="H47" s="12">
         <f>1000*H31/(H43*H13*H37)</f>
-        <v>4.7354398234877806</v>
+        <v>3.9580384524652037</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="13">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="U47">
         <f>(1.2*1000*H27*H25*H7*(1-H21))/(H13*H15*H23*(H9*H9-H11*H11)*(1-0.5*H21)*H17)</f>
-        <v>4.7354398234877815</v>
+        <v>3.9580384524652041</v>
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="42"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="G48" s="17"/>
       <c r="H48" s="18">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I48" s="18"/>
       <c r="J48" s="19">
@@ -2197,7 +2197,7 @@
       <c r="G49" s="21"/>
       <c r="H49" s="22">
         <f>H43/(2*H23*H37*H35*(1-H19))</f>
-        <v>2.3997558593749995</v>
+        <v>2.8710937499999991</v>
       </c>
       <c r="I49" s="22"/>
       <c r="J49" s="23">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="U49">
         <f>((H9*H9-H11*H11)*H15*((1-H21)^2))/(1.2*2*(1-0.5*H21)*H17*H17*H21*(1-H19))</f>
-        <v>2.3997558593749999</v>
+        <v>2.87109375</v>
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
@@ -2236,6 +2236,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2252,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67283A3-73B9-4307-B461-5D53218FFA00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69089A0A-99F5-4616-8013-B6640EB9D190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="q" sheetId="8" r:id="rId1"/>
@@ -733,6 +733,18 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -781,15 +793,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,9 +800,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="35"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
-      <c r="L8" s="41"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="44"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="39"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="40"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="41"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="45"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" s="9"/>
       <c r="H11" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9">
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="41"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="45"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="41"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="45"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="41"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="45"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="44"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="48"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="41"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="45"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="44"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="47"/>
+      <c r="L22" s="48"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="46"/>
-      <c r="D24" s="46"/>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="46"/>
-      <c r="L24" s="47"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="51"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
-      <c r="J26" s="49"/>
-      <c r="K26" s="49"/>
-      <c r="L26" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
+      <c r="L26" s="54"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="55"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="55"/>
-      <c r="H28" s="55"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="55"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="56"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="57"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="51"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="53"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="37"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="53"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="37"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1792,17 +1792,17 @@
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="53"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="37"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1840,17 +1840,17 @@
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
-      <c r="J36" s="57"/>
-      <c r="K36" s="57"/>
-      <c r="L36" s="57"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1888,17 +1888,17 @@
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="53"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="37"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1921,7 +1921,7 @@
       <c r="G39" s="11"/>
       <c r="H39" s="12">
         <f>H23*(H9*H9-H11*H11)</f>
-        <v>11304</v>
+        <v>10048</v>
       </c>
       <c r="I39" s="12"/>
       <c r="J39" s="13">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="53"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="37"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1969,7 +1969,7 @@
       <c r="G41" s="11"/>
       <c r="H41" s="12">
         <f>H15*H39</f>
-        <v>16956</v>
+        <v>15072</v>
       </c>
       <c r="I41" s="12"/>
       <c r="J41" s="13">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52"/>
-      <c r="D42" s="52"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="52"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="52"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="53"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="37"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2017,7 +2017,7 @@
       <c r="G43" s="11"/>
       <c r="H43" s="12">
         <f t="shared" si="1"/>
-        <v>14130</v>
+        <v>12560</v>
       </c>
       <c r="I43" s="12"/>
       <c r="J43" s="13">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="36"/>
+      <c r="K44" s="36"/>
+      <c r="L44" s="37"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2065,7 +2065,7 @@
       <c r="G45" s="11"/>
       <c r="H45" s="12">
         <f t="shared" si="2"/>
-        <v>2826</v>
+        <v>2512</v>
       </c>
       <c r="I45" s="12"/>
       <c r="J45" s="13">
@@ -2080,20 +2080,20 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="52"/>
-      <c r="I46" s="52"/>
-      <c r="J46" s="52"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="53"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="H46" s="36"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
+      <c r="K46" s="36"/>
+      <c r="L46" s="37"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="41" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2113,7 +2113,7 @@
       <c r="G47" s="11"/>
       <c r="H47" s="12">
         <f>1000*H31/(H43*H13*H37)</f>
-        <v>3.9580384524652037</v>
+        <v>4.4527932590233537</v>
       </c>
       <c r="I47" s="12"/>
       <c r="J47" s="13">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="U47">
         <f>(1.2*1000*H27*H25*H7*(1-H21))/(H13*H15*H23*(H9*H9-H11*H11)*(1-0.5*H21)*H17)</f>
-        <v>3.9580384524652041</v>
+        <v>4.4527932590233545</v>
       </c>
       <c r="W47">
         <f t="shared" ref="W47:Y47" si="3">(1.2*1000*J27*J25*J7*(1-J21))/(J13*J15*J23*(J9*J9-J11*J11)*(1-0.5*J21)*J17)</f>
@@ -2151,7 +2151,7 @@
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="38"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2197,7 +2197,7 @@
       <c r="G49" s="21"/>
       <c r="H49" s="22">
         <f>H43/(2*H23*H37*H35*(1-H19))</f>
-        <v>2.8710937499999991</v>
+        <v>2.5520833333333326</v>
       </c>
       <c r="I49" s="22"/>
       <c r="J49" s="23">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="U49">
         <f>((H9*H9-H11*H11)*H15*((1-H21)^2))/(1.2*2*(1-0.5*H21)*H17*H17*H21*(1-H19))</f>
-        <v>2.87109375</v>
+        <v>2.5520833333333335</v>
       </c>
       <c r="W49">
         <f t="shared" ref="W49:Y49" si="4">((J9*J9-J11*J11)*J15*((1-J21)^2))/(1.2*2*(1-0.5*J21)*J17*J17*J21*(1-J19))</f>
@@ -2236,12 +2236,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2258,6 +2252,12 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Лаб.работа/Расчет фрикционных элементов управления.xlsx
+++ b/Лаб.работа/Расчет фрикционных элементов управления.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BMSTU Projects\ПКП\Лаб.работа\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69089A0A-99F5-4616-8013-B6640EB9D190}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9C14D9-A065-43E3-85BB-9A740F21A901}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5805" yWindow="1935" windowWidth="19245" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -733,18 +733,6 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -793,6 +781,15 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -800,6 +797,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1120,16 +1120,16 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:14" ht="18" x14ac:dyDescent="0.25">
-      <c r="A4" s="39"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
     </row>
     <row r="5" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1"/>
@@ -1203,17 +1203,17 @@
     </row>
     <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A8" s="24"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="40"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
@@ -1245,17 +1245,17 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A10" s="24"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="45"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="40"/>
+      <c r="I10" s="40"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="41"/>
       <c r="N10" t="s">
         <v>28</v>
       </c>
@@ -1290,17 +1290,17 @@
     </row>
     <row r="12" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A12" s="24"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="41"/>
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
@@ -1336,17 +1336,17 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="24"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="45"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
+      <c r="L14" s="41"/>
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
@@ -1383,17 +1383,17 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A16" s="24"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="45"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="41"/>
     </row>
     <row r="17" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
@@ -1428,17 +1428,17 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="48"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="44"/>
     </row>
     <row r="19" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -1473,17 +1473,17 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" s="24"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="45"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="41"/>
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K21" s="32"/>
       <c r="L21" s="32">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="N21" t="s">
         <v>33</v>
@@ -1518,17 +1518,17 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="24"/>
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="47"/>
-      <c r="K22" s="47"/>
-      <c r="L22" s="48"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="44"/>
     </row>
     <row r="23" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
@@ -1560,17 +1560,17 @@
     </row>
     <row r="24" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
-      <c r="L24" s="51"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="46"/>
+      <c r="L24" s="47"/>
     </row>
     <row r="25" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
@@ -1606,17 +1606,17 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="24"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="53"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53"/>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
-      <c r="L26" s="54"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
@@ -1648,17 +1648,17 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="26"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="57"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="55"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="55"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="55"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="56"/>
     </row>
     <row r="29" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="27" t="s">
@@ -1696,17 +1696,17 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A30" s="27"/>
-      <c r="B30" s="35"/>
-      <c r="C30" s="36"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="37"/>
+      <c r="B30" s="51"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="53"/>
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
@@ -1744,17 +1744,17 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.2">
       <c r="A32" s="27"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="37"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="53"/>
     </row>
     <row r="33" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
@@ -1787,22 +1787,22 @@
       <c r="K33" s="11"/>
       <c r="L33" s="11">
         <f>L17/(1-L21)</f>
-        <v>102.27272727272727</v>
+        <v>101.12359550561797</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="27"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="37"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="53"/>
     </row>
     <row r="35" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="27" t="s">
@@ -1835,22 +1835,22 @@
       <c r="K35" s="10"/>
       <c r="L35" s="10">
         <f>L33-L17</f>
-        <v>12.272727272727266</v>
+        <v>11.123595505617971</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="28"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="38"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="38"/>
-      <c r="L36" s="38"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
     </row>
     <row r="37" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
@@ -1883,22 +1883,22 @@
       <c r="K37" s="13"/>
       <c r="L37" s="13">
         <f>(L17+L33)/2</f>
-        <v>96.136363636363626</v>
+        <v>95.561797752808985</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A38" s="29"/>
-      <c r="B38" s="35"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="37"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="53"/>
     </row>
     <row r="39" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A39" s="27" t="s">
@@ -1936,17 +1936,17 @@
     </row>
     <row r="40" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="27"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="36"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="37"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="53"/>
     </row>
     <row r="41" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A41" s="27" t="s">
@@ -1984,17 +1984,17 @@
     </row>
     <row r="42" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A42" s="27"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="37"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="53"/>
     </row>
     <row r="43" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A43" s="27" t="s">
@@ -2032,17 +2032,17 @@
     </row>
     <row r="44" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A44" s="27"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="36"/>
-      <c r="F44" s="36"/>
-      <c r="G44" s="36"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="37"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="27" t="s">
@@ -2080,20 +2080,20 @@
     </row>
     <row r="46" spans="1:25" ht="18" x14ac:dyDescent="0.2">
       <c r="A46" s="27"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="37"/>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="53"/>
     </row>
     <row r="47" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="10">
@@ -2123,7 +2123,7 @@
       <c r="K47" s="13"/>
       <c r="L47" s="13">
         <f>1000*L31/(L43*L13*L37)</f>
-        <v>5.1243393413741698</v>
+        <v>5.1551494624743031</v>
       </c>
       <c r="O47">
         <f>(1.2*1000*B27*B25*B7*(1-B21))/(B13*B15*B23*(B9*B9-B11*B11)*(1-0.5*B21)*B17)</f>
@@ -2147,11 +2147,11 @@
       </c>
       <c r="Y47">
         <f t="shared" si="3"/>
-        <v>5.1243393413741698</v>
+        <v>5.1551494624743031</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="18" x14ac:dyDescent="0.2">
-      <c r="A48" s="42"/>
+      <c r="A48" s="38"/>
       <c r="B48" s="16">
         <v>2</v>
       </c>
@@ -2207,7 +2207,7 @@
       <c r="K49" s="23"/>
       <c r="L49" s="23">
         <f>L43/(2*L23*L37*L35*(1-L19))</f>
-        <v>2.3307941511251218</v>
+        <v>2.5870403030896876</v>
       </c>
       <c r="O49">
         <f>((B9*B9-B11*B11)*B15*((1-B21)^2))/(1.2*2*(1-0.5*B21)*B17*B17*B21*(1-B19))</f>
@@ -2231,11 +2231,17 @@
       </c>
       <c r="Y49">
         <f t="shared" si="4"/>
-        <v>2.3307941511251205</v>
+        <v>2.5870403030896862</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B46:L46"/>
+    <mergeCell ref="B36:L36"/>
+    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B42:L42"/>
+    <mergeCell ref="B44:L44"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A47:A48"/>
     <mergeCell ref="B8:L8"/>
@@ -2252,12 +2258,6 @@
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B34:L34"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B36:L36"/>
-    <mergeCell ref="B38:L38"/>
-    <mergeCell ref="B40:L40"/>
-    <mergeCell ref="B42:L42"/>
-    <mergeCell ref="B44:L44"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
